--- a/data/trans_camb/DC-Clase-trans_camb.xlsx
+++ b/data/trans_camb/DC-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,35; -3,96</t>
+          <t>-13,0; -3,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,54; -0,82</t>
+          <t>-9,81; -0,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 6,81</t>
+          <t>-2,6; 6,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,05; 5,17</t>
+          <t>-8,43; 4,91</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-14,55; -3,34</t>
+          <t>-14,78; -3,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,52; 19,32</t>
+          <t>6,97; 18,88</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-8,89; -1,69</t>
+          <t>-8,82; -1,71</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-10,24; -2,85</t>
+          <t>-10,43; -3,09</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,67; 11,58</t>
+          <t>3,78; 11,54</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-66,9; -26,74</t>
+          <t>-68,3; -28,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-56,58; -6,15</t>
+          <t>-52,37; -4,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-14,6; 49,68</t>
+          <t>-14,81; 49,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-33,52; 30,43</t>
+          <t>-33,56; 28,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-61,34; -19,33</t>
+          <t>-60,78; -16,32</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,42; 112,05</t>
+          <t>28,65; 107,95</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-45,48; -10,68</t>
+          <t>-45,97; -10,85</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-51,41; -16,77</t>
+          <t>-51,87; -18,27</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>18,86; 72,5</t>
+          <t>18,87; 72,08</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,26; 2,34</t>
+          <t>-6,4; 2,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,28; -1,39</t>
+          <t>-9,53; -1,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,1; 12,8</t>
+          <t>3,1; 12,82</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-16,38; -3,57</t>
+          <t>-17,32; -3,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-18,42; -6,2</t>
+          <t>-18,32; -6,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 12,25</t>
+          <t>-0,67; 12,05</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-10,99; -2,6</t>
+          <t>-10,88; -2,9</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-12,93; -5,24</t>
+          <t>-12,93; -5,29</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,05; 10,44</t>
+          <t>2,39; 10,42</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-47,72; 27,12</t>
+          <t>-48,01; 27,7</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-69,66; -12,34</t>
+          <t>-70,41; -10,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22,08; 145,16</t>
+          <t>19,9; 138,45</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-50,59; -13,55</t>
+          <t>-53,24; -14,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-56,69; -22,82</t>
+          <t>-56,62; -23,31</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 46,13</t>
+          <t>-2,53; 45,48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-48,18; -13,98</t>
+          <t>-48,26; -16,19</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-56,77; -28,29</t>
+          <t>-56,27; -27,36</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,71; 58,51</t>
+          <t>10,57; 57,85</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-12,71; -4,16</t>
+          <t>-12,89; -4,27</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-15,91; -7,35</t>
+          <t>-15,5; -7,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-18,13; 6,25</t>
+          <t>-15,0; 6,67</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-16,54; 0,98</t>
+          <t>-17,23; 0,99</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-14,99; 4,03</t>
+          <t>-14,45; 4,49</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,06; 24,73</t>
+          <t>3,75; 22,91</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-11,65; -3,88</t>
+          <t>-11,96; -4,04</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-13,58; -5,73</t>
+          <t>-14,25; -6,15</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-15,97; 8,93</t>
+          <t>-14,27; 9,03</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-56,24; -23,46</t>
+          <t>-57,33; -23,27</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-69,4; -40,08</t>
+          <t>-68,87; -39,18</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-73,35; 32,33</t>
+          <t>-68,39; 34,26</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-45,21; 4,8</t>
+          <t>-46,66; 4,39</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-42,54; 15,94</t>
+          <t>-43,13; 19,61</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12,82; 96,61</t>
+          <t>9,91; 89,89</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-47,06; -18,71</t>
+          <t>-47,31; -18,92</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-55,79; -28,17</t>
+          <t>-56,49; -29,44</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-61,13; 41,38</t>
+          <t>-55,81; 40,95</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-11,67; -5,77</t>
+          <t>-11,76; -5,44</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-13,95; -7,95</t>
+          <t>-14,0; -8,22</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 5,85</t>
+          <t>-0,86; 6,16</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-12,56; -3,33</t>
+          <t>-12,84; -3,62</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-17,01; -8,4</t>
+          <t>-17,49; -8,49</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,41; 45,09</t>
+          <t>4,33; 40,43</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-10,89; -5,49</t>
+          <t>-10,99; -5,76</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-14,05; -9,2</t>
+          <t>-13,94; -8,95</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,64; 28,42</t>
+          <t>3,59; 32,22</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-50,38; -28,68</t>
+          <t>-50,55; -26,6</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-60,33; -39,74</t>
+          <t>-60,94; -41,05</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 29,09</t>
+          <t>-3,75; 30,81</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-38,61; -11,75</t>
+          <t>-39,59; -13,24</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-52,93; -30,52</t>
+          <t>-53,81; -30,45</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,81; 158,52</t>
+          <t>14,05; 141,07</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-41,34; -23,17</t>
+          <t>-41,92; -24,55</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-53,64; -38,46</t>
+          <t>-53,64; -38,03</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>13,98; 119,67</t>
+          <t>14,0; 132,01</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-15,67; -5,79</t>
+          <t>-15,69; -5,35</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-11,49; -1,92</t>
+          <t>-11,9; -1,68</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 10,9</t>
+          <t>-0,87; 11,2</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-5,85; 4,91</t>
+          <t>-4,93; 5,21</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-9,75; 0,55</t>
+          <t>-9,43; 0,33</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,9; 35,31</t>
+          <t>14,16; 33,64</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-8,23; -0,69</t>
+          <t>-8,36; -0,57</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-9,82; -2,42</t>
+          <t>-10,03; -2,47</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>10,15; 25,79</t>
+          <t>10,22; 25,94</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-65,51; -31,77</t>
+          <t>-66,36; -29,12</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-50,19; -12,23</t>
+          <t>-51,34; -10,42</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 63,71</t>
+          <t>-4,07; 65,97</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-18,74; 19,13</t>
+          <t>-16,5; 20,82</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-32,0; 1,98</t>
+          <t>-31,69; 0,14</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>45,46; 133,67</t>
+          <t>46,87; 132,67</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-30,86; -3,23</t>
+          <t>-30,32; -2,46</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-35,84; -10,42</t>
+          <t>-37,2; -11,29</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>36,87; 109,18</t>
+          <t>38,9; 113,36</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 3,99</t>
+          <t>-1,51; 4,41</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 0,87</t>
+          <t>-3,25; 0,82</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3,27; 16,67</t>
+          <t>3,0; 16,59</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 1,81</t>
+          <t>-5,61; 1,46</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-13,62; -6,75</t>
+          <t>-13,36; -6,44</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,3; 13,26</t>
+          <t>4,92; 12,83</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 1,42</t>
+          <t>-4,75; 1,47</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-11,3; -5,47</t>
+          <t>-11,4; -5,84</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>4,01; 11,33</t>
+          <t>3,82; 11,36</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-60,17; 326,04</t>
+          <t>-60,22; 465,71</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 115,6</t>
+          <t>-100,0; 192,31</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>62,82; 1266,89</t>
+          <t>70,5; 1204,86</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-19,39; 6,89</t>
+          <t>-19,67; 5,73</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-46,06; -25,6</t>
+          <t>-45,93; -25,14</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>17,91; 51,48</t>
+          <t>16,34; 49,35</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-18,38; 6,71</t>
+          <t>-19,39; 6,78</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-47,33; -25,59</t>
+          <t>-47,59; -26,41</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>16,95; 53,29</t>
+          <t>15,39; 52,89</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-8,83; -5,47</t>
+          <t>-8,87; -5,44</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-9,52; -6,19</t>
+          <t>-9,7; -6,34</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 5,06</t>
+          <t>-1,75; 4,93</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-6,4; -2,15</t>
+          <t>-6,25; -1,97</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-11,55; -7,6</t>
+          <t>-11,75; -7,59</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>10,65; 26,66</t>
+          <t>10,42; 25,36</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-7,08; -4,27</t>
+          <t>-6,93; -4,1</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-10,22; -7,51</t>
+          <t>-10,19; -7,41</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>5,67; 16,7</t>
+          <t>5,47; 15,62</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-48,2; -32,96</t>
+          <t>-48,15; -32,7</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-52,3; -37,75</t>
+          <t>-52,03; -37,87</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-8,62; 30,61</t>
+          <t>-10,06; 28,58</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-21,95; -7,92</t>
+          <t>-21,73; -7,62</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-39,95; -28,18</t>
+          <t>-40,21; -27,87</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>37,21; 97,83</t>
+          <t>36,74; 92,41</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-30,0; -19,21</t>
+          <t>-29,65; -18,82</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-43,13; -33,74</t>
+          <t>-43,44; -33,54</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>24,32; 72,06</t>
+          <t>23,47; 68,46</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/DC-Clase-trans_camb.xlsx
+++ b/data/trans_camb/DC-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,97</t>
+          <t>2,13</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,3</t>
+          <t>13,6</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>7,68</t>
+          <t>7,91</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-13,0; -3,87</t>
+          <t>-12,37; -3,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,81; -0,65</t>
+          <t>-9,57; -0,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 6,77</t>
+          <t>-2,73; 6,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,43; 4,91</t>
+          <t>-8,31; 4,98</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-14,78; -3,0</t>
+          <t>-14,81; -3,24</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,97; 18,88</t>
+          <t>7,31; 19,25</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-8,82; -1,71</t>
+          <t>-9,4; -1,94</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-10,43; -3,09</t>
+          <t>-9,83; -2,79</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,78; 11,54</t>
+          <t>4,39; 11,79</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>63,2%</t>
+          <t>64,61%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>44,01%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-68,3; -28,76</t>
+          <t>-67,82; -29,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-52,37; -4,31</t>
+          <t>-53,01; -5,03</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-14,81; 49,03</t>
+          <t>-15,24; 50,13</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-33,56; 28,9</t>
+          <t>-33,93; 27,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-60,78; -16,32</t>
+          <t>-60,45; -16,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,65; 107,95</t>
+          <t>28,17; 110,1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-45,97; -10,85</t>
+          <t>-46,7; -10,97</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-51,87; -18,27</t>
+          <t>-50,26; -17,71</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>18,87; 72,08</t>
+          <t>21,4; 73,21</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8,0</t>
+          <t>7,71</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,97</t>
+          <t>6,96</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>6,26</t>
+          <t>6,7</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,4; 2,43</t>
+          <t>-6,26; 2,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,53; -1,21</t>
+          <t>-9,59; -1,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,1; 12,82</t>
+          <t>2,74; 12,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-17,32; -3,98</t>
+          <t>-16,67; -3,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-18,32; -6,13</t>
+          <t>-18,66; -6,35</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 12,05</t>
+          <t>0,55; 13,46</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-10,88; -2,9</t>
+          <t>-10,49; -2,79</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-12,93; -5,29</t>
+          <t>-12,85; -5,29</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,39; 10,42</t>
+          <t>2,63; 11,02</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>70,17%</t>
+          <t>67,66%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>32,7%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-48,01; 27,7</t>
+          <t>-46,73; 27,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-70,41; -10,97</t>
+          <t>-67,6; -12,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19,9; 138,45</t>
+          <t>17,57; 138,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-53,24; -14,91</t>
+          <t>-51,43; -13,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-56,62; -23,31</t>
+          <t>-56,83; -23,93</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 45,48</t>
+          <t>1,61; 52,98</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-48,26; -16,19</t>
+          <t>-47,78; -15,15</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-56,27; -27,36</t>
+          <t>-56,32; -26,78</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10,57; 57,85</t>
+          <t>11,41; 62,38</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-4,4</t>
+          <t>4,48</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,45</t>
+          <t>14,77</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-1,0</t>
+          <t>7,9</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-12,89; -4,27</t>
+          <t>-12,83; -4,38</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-15,5; -7,15</t>
+          <t>-15,62; -7,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-15,0; 6,67</t>
+          <t>-1,01; 9,61</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-17,23; 0,99</t>
+          <t>-17,21; 1,36</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-14,45; 4,49</t>
+          <t>-15,08; 4,43</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,75; 22,91</t>
+          <t>5,75; 24,46</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-11,96; -4,04</t>
+          <t>-11,86; -3,89</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-14,25; -6,15</t>
+          <t>-14,03; -5,72</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-14,27; 9,03</t>
+          <t>3,21; 12,36</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-21,73%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>47,49%</t>
+          <t>48,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-4,42%</t>
+          <t>34,89%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-57,33; -23,27</t>
+          <t>-56,57; -24,14</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-68,87; -39,18</t>
+          <t>-68,56; -38,79</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-68,39; 34,26</t>
+          <t>-4,65; 54,29</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-46,66; 4,39</t>
+          <t>-47,09; 6,05</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-43,13; 19,61</t>
+          <t>-44,13; 17,93</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,91; 89,89</t>
+          <t>15,16; 98,35</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-47,31; -18,92</t>
+          <t>-48,02; -18,86</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-56,49; -29,44</t>
+          <t>-56,9; -27,47</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-55,81; 40,95</t>
+          <t>12,79; 60,96</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2,5</t>
+          <t>1,93</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,48</t>
+          <t>6,63</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>11,76</t>
+          <t>4,52</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-11,76; -5,44</t>
+          <t>-11,81; -5,83</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-14,0; -8,22</t>
+          <t>-14,19; -8,49</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 6,16</t>
+          <t>-1,55; 5,34</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-12,84; -3,62</t>
+          <t>-12,73; -3,46</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-17,49; -8,49</t>
+          <t>-17,12; -8,2</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,33; 40,43</t>
+          <t>2,47; 11,2</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-10,99; -5,76</t>
+          <t>-10,95; -5,62</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-13,94; -8,95</t>
+          <t>-14,13; -9,17</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,59; 32,22</t>
+          <t>1,84; 7,44</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>64,78%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>18,26%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-50,55; -26,6</t>
+          <t>-50,51; -28,52</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-60,94; -41,05</t>
+          <t>-60,22; -40,72</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 30,81</t>
+          <t>-6,55; 26,37</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-39,59; -13,24</t>
+          <t>-39,39; -12,29</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-53,81; -30,45</t>
+          <t>-52,69; -29,63</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,05; 141,07</t>
+          <t>7,28; 40,77</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-41,92; -24,55</t>
+          <t>-42,16; -24,62</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-53,64; -38,03</t>
+          <t>-53,68; -38,12</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>14,0; 132,01</t>
+          <t>7,02; 31,87</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5,08</t>
+          <t>3,82</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>21,4</t>
+          <t>18,0</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>15,67</t>
+          <t>12,05</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-15,69; -5,35</t>
+          <t>-15,43; -5,66</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-11,9; -1,68</t>
+          <t>-11,81; -1,95</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 11,2</t>
+          <t>-1,47; 9,37</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,93; 5,21</t>
+          <t>-5,49; 4,35</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-9,43; 0,33</t>
+          <t>-9,84; 0,16</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>14,16; 33,64</t>
+          <t>12,83; 22,38</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-8,36; -0,57</t>
+          <t>-8,32; -0,62</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-10,03; -2,47</t>
+          <t>-9,55; -2,75</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>10,22; 25,94</t>
+          <t>8,49; 15,77</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>64,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>62,99%</t>
+          <t>48,45%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-66,36; -29,12</t>
+          <t>-66,15; -31,4</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-51,34; -10,42</t>
+          <t>-50,5; -11,09</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 65,97</t>
+          <t>-7,55; 54,89</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-16,5; 20,82</t>
+          <t>-17,94; 17,2</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-31,69; 0,14</t>
+          <t>-32,82; 0,14</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>46,87; 132,67</t>
+          <t>40,14; 90,84</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-30,32; -2,46</t>
+          <t>-30,83; -2,94</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-37,2; -11,29</t>
+          <t>-36,17; -11,51</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>38,9; 113,36</t>
+          <t>31,34; 69,13</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8,58</t>
+          <t>8,6</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,99</t>
+          <t>8,54</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>7,7</t>
+          <t>7,88</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 4,41</t>
+          <t>-1,57; 4,15</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 0,82</t>
+          <t>-3,43; 0,99</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3,0; 16,59</t>
+          <t>3,43; 16,14</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-5,61; 1,46</t>
+          <t>-5,51; 1,84</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-13,36; -6,44</t>
+          <t>-13,35; -6,73</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,92; 12,83</t>
+          <t>4,92; 12,49</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 1,47</t>
+          <t>-4,59; 1,54</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-11,4; -5,84</t>
+          <t>-11,5; -5,81</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>3,82; 11,36</t>
+          <t>4,14; 11,27</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>384,97%</t>
+          <t>386,08%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>34,84%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-60,22; 465,71</t>
+          <t>-57,51; 334,85</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 192,31</t>
+          <t>-92,01; 126,32</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>70,5; 1204,86</t>
+          <t>62,92; 1165,45</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-19,67; 5,73</t>
+          <t>-18,8; 6,9</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-45,93; -25,14</t>
+          <t>-45,98; -25,81</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>16,34; 49,35</t>
+          <t>17,07; 48,41</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-19,39; 6,78</t>
+          <t>-19,09; 7,03</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-47,59; -26,41</t>
+          <t>-47,81; -27,03</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>15,39; 52,89</t>
+          <t>17,82; 53,06</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2,63</t>
+          <t>3,9</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>15,19</t>
+          <t>10,89</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>9,16</t>
+          <t>7,55</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-8,87; -5,44</t>
+          <t>-8,91; -5,57</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-9,7; -6,34</t>
+          <t>-9,75; -6,35</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 4,93</t>
+          <t>2,04; 6,03</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-6,25; -1,97</t>
+          <t>-6,22; -1,96</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-11,75; -7,59</t>
+          <t>-11,5; -7,44</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>10,42; 25,36</t>
+          <t>8,75; 12,97</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-6,93; -4,1</t>
+          <t>-6,85; -4,23</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-10,19; -7,41</t>
+          <t>-10,08; -7,39</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>5,47; 15,62</t>
+          <t>6,1; 8,96</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>39,07%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>33,14%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-48,15; -32,7</t>
+          <t>-48,3; -33,4</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-52,03; -37,87</t>
+          <t>-52,43; -38,1</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-10,06; 28,58</t>
+          <t>11,11; 36,19</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-21,73; -7,62</t>
+          <t>-21,33; -7,24</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-40,21; -27,87</t>
+          <t>-39,75; -27,49</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>36,74; 92,41</t>
+          <t>29,8; 48,55</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-29,65; -18,82</t>
+          <t>-29,32; -19,06</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-43,44; -33,54</t>
+          <t>-42,76; -33,64</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>23,47; 68,46</t>
+          <t>26,03; 40,94</t>
         </is>
       </c>
     </row>
